--- a/XBRL-template-MFRS/Company/08-SOCF-Direct.xlsx
+++ b/XBRL-template-MFRS/Company/08-SOCF-Direct.xlsx
@@ -793,11 +793,11 @@
         </is>
       </c>
       <c r="B20" s="35">
-        <f>1*B8+1*B9+1*B10+1*B11+-1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+-1*B18+1*B19</f>
+        <f>1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19</f>
         <v/>
       </c>
       <c r="C20" s="35">
-        <f>1*C8+1*C9+1*C10+1*C11+-1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+-1*C18+1*C19</f>
+        <f>1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19</f>
         <v/>
       </c>
       <c r="D20" s="36" t="n"/>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B52" s="35">
-        <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+-1*B30+-1*B31+1*B32+1*B33+-1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+1*B48+1*B49+1*B50+1*B51</f>
+        <f>1*B22+-1*B23+1*B24+-1*B25+1*B26+-1*B27+1*B28+-1*B29+1*B30+-1*B31+1*B32+-1*B33+1*B34+1*B35+1*B36+1*B37+1*B38+1*B39+-1*B40+-1*B41+-1*B42+1*B43+1*B44+1*B45+-1*B46+-1*B47+-1*B48+-1*B49+1*B50+1*B51</f>
         <v/>
       </c>
       <c r="C52" s="35">
-        <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+-1*C30+-1*C31+1*C32+1*C33+-1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+1*C48+1*C49+1*C50+1*C51</f>
+        <f>1*C22+-1*C23+1*C24+-1*C25+1*C26+-1*C27+1*C28+-1*C29+1*C30+-1*C31+1*C32+-1*C33+1*C34+1*C35+1*C36+1*C37+1*C38+1*C39+-1*C40+-1*C41+-1*C42+1*C43+1*C44+1*C45+-1*C46+-1*C47+-1*C48+-1*C49+1*C50+1*C51</f>
         <v/>
       </c>
       <c r="D52" s="36" t="n"/>
@@ -1325,11 +1325,11 @@
         </is>
       </c>
       <c r="B72" s="28">
-        <f>-1*B54+-1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+-1*B63+1*B64+-1*B65+-1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
+        <f>1*B54+1*B55+1*B56+1*B57+1*B58+1*B59+-1*B60+-1*B61+-1*B62+1*B63+1*B64+-1*B65+1*B66+1*B67+1*B68+-1*B69+-1*B70+1*B71</f>
         <v/>
       </c>
       <c r="C72" s="28">
-        <f>-1*C54+-1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+-1*C63+1*C64+-1*C65+-1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
+        <f>1*C54+1*C55+1*C56+1*C57+1*C58+1*C59+-1*C60+-1*C61+-1*C62+1*C63+1*C64+-1*C65+1*C66+1*C67+1*C68+-1*C69+-1*C70+1*C71</f>
         <v/>
       </c>
       <c r="D72" s="33" t="n"/>
